--- a/models/sovereigns/Mozambique_Sovereign_Model.xlsx
+++ b/models/sovereigns/Mozambique_Sovereign_Model.xlsx
@@ -637,15 +637,29 @@
           <t>policy_rate_pct</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
+      <c r="B3" s="2" t="n">
+        <v>9.25</v>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sep-26</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Banco de Moçambique, MIMO rate decision</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>25-Sep-26</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -671,15 +685,29 @@
           <t>cpi_latest_yoy_pct</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
+      <c r="B5" s="2" t="n">
+        <v>6.5</v>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Aug-26</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>INE, Consumer Price Index Bulletin</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10-Sep-26</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -741,7 +769,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>106.1</v>
+        <v>94</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -750,12 +778,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF WEO</t>
+          <t>Adjudicated document (View), approximate</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -765,7 +793,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+          <t>public debt, approximate, as stated in the document view</t>
         </is>
       </c>
     </row>
@@ -949,7 +977,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>3.843</v>
+        <v>3.9</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -958,22 +986,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Aug-26</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>World Bank WDI</t>
+          <t>Banco de Moçambique</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>31-Aug-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+          <t>gross international reserves</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1029,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>3.44</v>
+        <v>6.5</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1010,24 +1038,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Aug-26</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>World Bank WDI</t>
+          <t>Banco de Moçambique (excluding megaprojects)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+          <t>31-Aug-26</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1121,15 +1145,29 @@
           <t>eurobonds_outstanding_usd_bn</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n"/>
+      <c r="B23" s="2" t="n">
+        <v>0.9</v>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Jun-26</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ministry of Economy and Finance, Public Debt Bulletin</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Jun-26</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1211,6 +1249,16 @@
           <t>fitch</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>24-Jul-26</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1218,6 +1266,16 @@
           <t>sp</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CCC (LC: SD)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>25-Sep-26</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1225,11 +1283,41 @@
           <t>moodys</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Caa3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>18-Oct-24</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
           <t>IMF</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Extended Credit Facility (2022) lapsed Apr-25; successor under discussion</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>May-22 (SDR 340.8m)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>In debt distress</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Mozambique_Sovereign_Model.xlsx
+++ b/models/sovereigns/Mozambique_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/mozambique.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/mozambique.json</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Banco de Moçambique, MIMO rate decision</t>
+          <t>Banco de Moçambique, Monetary Policy Committee decision (MIMO rate)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -776,14 +776,10 @@
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Adjudicated document (View), approximate</t>
+          <t>Adjudicated document (View section, uncited)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -793,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>public debt, approximate, as stated in the document view</t>
+          <t>public debt, approximate; source and perimeter not cited in the document</t>
         </is>
       </c>
     </row>
@@ -1001,7 +997,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross international reserves</t>
+          <t>gross international reserves; gold treatment not stated</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1039,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Banco de Moçambique (excluding megaprojects)</t>
+          <t>Banco de Moçambique (excluding megaprojects imports)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1160,7 +1156,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance, Public Debt Bulletin</t>
+          <t>MEF, Public Debt Bulletin &amp; 2031 Eurobond Terms (US$900m 9.00% amortising notes due 15-Sep-31, XS2051203862)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1268,7 +1264,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CCC (LC: SD)</t>
+          <t>CCC (LTFC) / SD (LC)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1307,17 +1303,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Extended Credit Facility (2022) lapsed Apr-25; successor under discussion</t>
+          <t>2022 Extended Credit Facility (SDR 340.8m) lapsed Apr-25 with reviews incomplete; successor arrangement under discussion after Sep-26 staff mission</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>May-22 (SDR 340.8m)</t>
+          <t>May-22</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>In debt distress</t>
+          <t>In debt distress (IMF DSA, Sep-26)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Mozambique_Sovereign_Model.xlsx
+++ b/models/sovereigns/Mozambique_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 08-Oct-26</t>
+          <t>as of 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Banco de Moçambique, Monetary Policy Committee decision (MIMO rate)</t>
+          <t>Banco de Moçambique, MIMO policy rate decision</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross international reserves; gold treatment not stated</t>
+          <t>gross international reserves</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MEF, Public Debt Bulletin &amp; 2031 Eurobond Terms (US$900m 9.00% amortising notes due 15-Sep-31, XS2051203862)</t>
+          <t>Ministry of Economy and Finance, Public Debt Bulletin (sole bond: 9.00% amortising notes due 15-Sep-31, XS2051203862)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CCC (LTFC) / SD (LC)</t>
+          <t>CCC (local currency SD)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2022 Extended Credit Facility (SDR 340.8m) lapsed Apr-25 with reviews incomplete; successor arrangement under discussion after Sep-26 staff mission</t>
+          <t>None active; 2022 ECF (SDR 340.8m) lapsed Apr-25, successor arrangement under discussion after Sep-26 staff mission</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>May-22</t>
+          <t>May-22 (lapsed Apr-25)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">

--- a/models/sovereigns/Mozambique_Sovereign_Model.xlsx
+++ b/models/sovereigns/Mozambique_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Banco de Moçambique, MIMO policy rate decision</t>
+          <t>Banco de Moçambique, MIMO rate decision</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -779,7 +779,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Adjudicated document (View section, uncited)</t>
+          <t>Adjudicated report view (08-Oct-26), no primary citation</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>public debt, approximate; source and perimeter not cited in the document</t>
+          <t>approximate, public debt; underlying source not cited in report</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross international reserves</t>
+          <t>gross international reserves (components not specified)</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Banco de Moçambique (excluding megaprojects imports)</t>
+          <t>Banco de Moçambique (excluding megaprojects)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance, Public Debt Bulletin (sole bond: 9.00% amortising notes due 15-Sep-31, XS2051203862)</t>
+          <t>MEF, Public Debt Bulletin (9.00% amortising notes due 2031, XS2051203862)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CCC (local currency SD)</t>
+          <t>CCC (LC: SD)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>None active; 2022 ECF (SDR 340.8m) lapsed Apr-25, successor arrangement under discussion after Sep-26 staff mission</t>
+          <t>2022 ECF (SDR 340.8m) lapsed Apr-25 with fifth and sixth reviews uncompleted; successor arrangement under discussion after Sep-26 staff mission</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>May-22 (lapsed Apr-25)</t>
+          <t>May-22</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">

--- a/models/sovereigns/Mozambique_Sovereign_Model.xlsx
+++ b/models/sovereigns/Mozambique_Sovereign_Model.xlsx
@@ -776,10 +776,14 @@
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Adjudicated report view (08-Oct-26), no primary citation</t>
+          <t>Adjudicated document (run 2026-10-08_1751), approximate ~94% of GDP; underlying source not cited</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -789,7 +793,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>approximate, public debt; underlying source not cited in report</t>
+          <t>public debt, approximate, as stated in the adjudicated document view</t>
         </is>
       </c>
     </row>
@@ -997,7 +1001,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross international reserves (components not specified)</t>
+          <t>gross international reserves (as reported by Banco de Moçambique)</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1160,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MEF, Public Debt Bulletin (9.00% amortising notes due 2031, XS2051203862)</t>
+          <t>Ministry of Economy and Finance, Public Debt Bulletin (USD 900m 9.00% amortising notes due 15-Sep-31, XS2051203862)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jun-26</t>
+          <t>30-Jun-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1303,12 +1307,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2022 ECF (SDR 340.8m) lapsed Apr-25 with fifth and sixth reviews uncompleted; successor arrangement under discussion after Sep-26 staff mission</t>
+          <t>None; 2022 ECF (SDR 340.8m) lapsed Apr-25; successor arrangement under discussion after Sep-26 staff mission</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>May-22</t>
+          <t>May-22 (lapsed Apr-25)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1328,7 +1332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1342,6 +1346,11 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
@@ -1352,7 +1361,8 @@
           <t>nominal_gdp_usd_bn</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1360,7 +1370,8 @@
           <t>real_gdp_growth_pct</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1368,7 +1379,8 @@
           <t>cpi_avg_pct</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1376,7 +1388,8 @@
           <t>current_account_pct_gdp</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1384,7 +1397,8 @@
           <t>fiscal_balance_pct_gdp</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1392,7 +1406,8 @@
           <t>primary_balance_pct_gdp</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1400,7 +1415,8 @@
           <t>gov_debt_pct_gdp</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1408,7 +1424,8 @@
           <t>external_debt_pct_gdp</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1416,7 +1433,14 @@
           <t>gross_reserves_usd_bn</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Banco de Moçambique, 31-Aug-26 (Aug-26 point value, not a year-end figure)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1424,7 +1448,8 @@
           <t>revenue_pct_gdp</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1432,7 +1457,8 @@
           <t>interest_pct_revenue</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/models/sovereigns/Mozambique_Sovereign_Model.xlsx
+++ b/models/sovereigns/Mozambique_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Banco de Moçambique, MIMO rate decision</t>
+          <t>Banco de Moçambique, MPC decision (MIMO rate)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -776,14 +776,10 @@
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Adjudicated document (run 2026-10-08_1751), approximate ~94% of GDP; underlying source not cited</t>
+          <t>Adjudicated document, View section</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -793,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>public debt, approximate, as stated in the adjudicated document view</t>
+          <t>public debt, approximate, as stated in the adjudicated document view (no primary source cited)</t>
         </is>
       </c>
     </row>
@@ -1001,7 +997,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross international reserves (as reported by Banco de Moçambique)</t>
+          <t>gross international reserves (central bank; gold treatment not stated)</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1039,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Banco de Moçambique (excluding megaprojects)</t>
+          <t>Banco de Moçambique (excluding megaprojects imports)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1160,12 +1156,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance, Public Debt Bulletin (USD 900m 9.00% amortising notes due 15-Sep-31, XS2051203862)</t>
+          <t>MEF, Public Debt Bulletin (sole Eurobond, 9.00% due 15-Sep-31, XS2051203862; first amortisation 15-Sep-28)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>30-Jun-26</t>
+          <t>Jun-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1307,12 +1303,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>None; 2022 ECF (SDR 340.8m) lapsed Apr-25; successor arrangement under discussion after Sep-26 staff mission</t>
+          <t>2022 Extended Credit Facility (36-month; lapsed Apr-25 with fifth and sixth reviews uncompleted); successor arrangement under discussion after Sep-26 staff mission</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>May-22 (lapsed Apr-25)</t>
+          <t>May-22 (SDR 340.8m)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">

--- a/models/sovereigns/Mozambique_Sovereign_Model.xlsx
+++ b/models/sovereigns/Mozambique_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Banco de Moçambique, MPC decision (MIMO rate)</t>
+          <t>Banco de Moçambique, MIMO rate decision</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -779,7 +779,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Adjudicated document, View section</t>
+          <t>Adjudicated document view, run 2026-10-08_1751</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>public debt, approximate, as stated in the adjudicated document view (no primary source cited)</t>
+          <t>public debt, approximate; document gives no component or source attribution</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross international reserves (central bank; gold treatment not stated)</t>
+          <t>gross international reserves (gold treatment not stated)</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MEF, Public Debt Bulletin (sole Eurobond, 9.00% due 15-Sep-31, XS2051203862; first amortisation 15-Sep-28)</t>
+          <t>MEF, Public Debt Bulletin (9.00% Eurobond due 15-Sep-31, XS2051203862, sole Eurobond)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2022 Extended Credit Facility (36-month; lapsed Apr-25 with fifth and sixth reviews uncompleted); successor arrangement under discussion after Sep-26 staff mission</t>
+          <t>None current; 2022 ECF (SDR 340.8m) lapsed Apr-25 with 5th and 6th reviews uncompleted; successor arrangement under discussion after Sep-26 staff mission</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>May-22 (SDR 340.8m)</t>
+          <t>May-22 (ECF, SDR 340.8m)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">

--- a/models/sovereigns/Mozambique_Sovereign_Model.xlsx
+++ b/models/sovereigns/Mozambique_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/mozambique.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/mozambique.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Mozambique_Sovereign_Model.xlsx
+++ b/models/sovereigns/Mozambique_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/mozambique.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/mozambique.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Mozambique_Sovereign_Model.xlsx
+++ b/models/sovereigns/Mozambique_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/mozambique.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/mozambique.json</t>
         </is>
       </c>
     </row>
